--- a/developer-di-practitioner/10-mod3-excel-writer/files/Sales_and_Expenses_2017.xlsx
+++ b/developer-di-practitioner/10-mod3-excel-writer/files/Sales_and_Expenses_2017.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Sales Chart" r:id="rId1" sheetId="4"/>
     <sheet name="SourceData" r:id="rId2" sheetId="1"/>
   </sheets>
-  <calcPr calcId="171027" concurrentCalc="0"/>
+  <calcPr fullCalcOnLoad="1" calcId="171027" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="http://schemas.microsoft.com/office/mac/excel/2008/main">
       <mx:ArchID Flags="2"/>
@@ -3113,7 +3113,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="6" t="n">
-        <f ref="B10:G10" si="4" t="shared">B5+B6+B8</f>
+        <f ref="B10:G10" si="4" t="shared">SUM(B5:B8)</f>
         <v>35655.55</v>
       </c>
       <c r="C10" s="6" t="n">

--- a/developer-di-practitioner/10-mod3-excel-writer/files/Sales_and_Expenses_2017.xlsx
+++ b/developer-di-practitioner/10-mod3-excel-writer/files/Sales_and_Expenses_2017.xlsx
@@ -111,7 +111,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00&quot;€&quot;"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="yyyy"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
@@ -393,7 +393,7 @@
             <c:numRef>
               <c:f>SourceData!$B$5:$G$5</c:f>
               <c:numCache>
-                <c:formatCode>#,##0.00"€"</c:formatCode>
+                <c:formatCode>"$"#,##0.00</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>23455.22</c:v>
@@ -491,7 +491,7 @@
             <c:numRef>
               <c:f>SourceData!$B$6:$G$6</c:f>
               <c:numCache>
-                <c:formatCode>#,##0.00"€"</c:formatCode>
+                <c:formatCode>"$"#,##0.00</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>11244.21</c:v>
@@ -589,7 +589,7 @@
             <c:numRef>
               <c:f>SourceData!$B$7:$G$7</c:f>
               <c:numCache>
-                <c:formatCode>#,##0.00"€"</c:formatCode>
+                <c:formatCode>"$"#,##0.00</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>1231.29</c:v>
@@ -694,7 +694,7 @@
             <c:numRef>
               <c:f>SourceData!$B$8:$G$8</c:f>
               <c:numCache>
-                <c:formatCode>#,##0.00"€"</c:formatCode>
+                <c:formatCode>"$"#,##0.00</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>956.12</c:v>
@@ -869,7 +869,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="#,##0.00&quot;€&quot;" sourceLinked="1"/>
+        <c:numFmt formatCode="&quot;$&quot;#,##0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1278,7 +1278,7 @@
             <c:numRef>
               <c:f>SourceData!$H$5:$H$8</c:f>
               <c:numCache>
-                <c:formatCode>#,##0.00"€"</c:formatCode>
+                <c:formatCode>"$"#,##0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>132463.11000000002</c:v>
